--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N38_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N38_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>84.43792413624637</v>
+        <v>13.72116267214004</v>
       </c>
       <c r="D2" t="n">
-        <v>84.84904466502837</v>
+        <v>13.78796975806711</v>
       </c>
       <c r="E2" t="n">
-        <v>8.020829539379612</v>
+        <v>1.303384800149187</v>
       </c>
       <c r="F2" t="n">
-        <v>8.604001504107362</v>
+        <v>1.398150244417446</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>80.91582436882891</v>
+        <v>13.1488214599347</v>
       </c>
       <c r="D3" t="n">
-        <v>81.07017351232864</v>
+        <v>13.1739031957534</v>
       </c>
       <c r="E3" t="n">
-        <v>8.020829539379612</v>
+        <v>1.303384800149187</v>
       </c>
       <c r="F3" t="n">
-        <v>8.604001504107362</v>
+        <v>1.398150244417446</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>77.6203761689938</v>
+        <v>12.61331112746149</v>
       </c>
       <c r="D4" t="n">
-        <v>78.61059048685424</v>
+        <v>12.77422095411381</v>
       </c>
       <c r="E4" t="n">
-        <v>8.020829539379612</v>
+        <v>1.303384800149187</v>
       </c>
       <c r="F4" t="n">
-        <v>8.604001504107362</v>
+        <v>1.398150244417446</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>92.18729388014211</v>
+        <v>14.98043525552309</v>
       </c>
       <c r="D5" t="n">
-        <v>93.45906607667166</v>
+        <v>15.18709823745914</v>
       </c>
       <c r="E5" t="n">
-        <v>8.020829539379612</v>
+        <v>1.303384800149187</v>
       </c>
       <c r="F5" t="n">
-        <v>8.604001504107362</v>
+        <v>1.398150244417446</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>67.80563384683826</v>
+        <v>11.01841550011122</v>
       </c>
       <c r="D6" t="n">
-        <v>67.05772725546429</v>
+        <v>10.89688067901295</v>
       </c>
       <c r="E6" t="n">
-        <v>8.020829539379612</v>
+        <v>1.303384800149187</v>
       </c>
       <c r="F6" t="n">
-        <v>8.604001504107362</v>
+        <v>1.398150244417446</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
